--- a/hall/resources/sample/PoolList.xlsx
+++ b/hall/resources/sample/PoolList.xlsx
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>卡池ID</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>卡池类型</t>
+  </si>
+  <si>
+    <t>抽奖消耗</t>
   </si>
   <si>
     <t>掉落物品</t>
@@ -109,6 +112,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>map&lt;int{_}long&gt;{|}</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -119,6 +125,9 @@
   </si>
   <si>
     <t>type</t>
+  </si>
+  <si>
+    <t>DrawCost</t>
   </si>
   <si>
     <t>DropItem</t>
@@ -136,10 +145,16 @@
     <t>游客卡池1</t>
   </si>
   <si>
+    <t>1024013_1</t>
+  </si>
+  <si>
     <t>游客卡池2</t>
   </si>
   <si>
     <t>雇员卡池1</t>
+  </si>
+  <si>
+    <t>1024014_1</t>
   </si>
   <si>
     <t>主包ID</t>
@@ -344,12 +359,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1367,14 +1382,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="4" max="4" width="18.5" customWidth="1"/>
-    <col min="5" max="5" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="20.25" customWidth="1"/>
+    <col min="5" max="5" width="18.5" customWidth="1"/>
+    <col min="6" max="6" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1396,50 +1412,59 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>17</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1447,65 +1472,75 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="3">
         <v>10001</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3">
         <v>1001</v>
       </c>
-      <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="3" t="b">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6" s="3">
         <v>10002</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3">
         <v>1002</v>
       </c>
-      <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="3" t="b">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7" s="3">
         <v>20001</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3">
         <v>2</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="3">
         <v>2001</v>
       </c>
-      <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="3" t="b">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1513,8 +1548,9 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1522,8 +1558,9 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1531,8 +1568,9 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1540,8 +1578,9 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1549,8 +1588,9 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1558,8 +1598,9 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1567,8 +1608,9 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1576,6 +1618,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1595,37 +1638,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:11">

--- a/hall/resources/sample/PoolList.xlsx
+++ b/hall/resources/sample/PoolList.xlsx
@@ -1382,15 +1382,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="20.25" customWidth="1"/>
     <col min="5" max="5" width="18.5" customWidth="1"/>
     <col min="6" max="6" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:8">
+    <row r="2" ht="18" customHeight="1" spans="1:9">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1440,7 +1440,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1474,7 +1474,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="3">
         <v>10001</v>
       </c>
@@ -1493,10 +1493,10 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="3">
         <v>10002</v>
       </c>
@@ -1515,10 +1515,11 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="3">
         <v>20001</v>
       </c>
@@ -1540,7 +1541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1550,7 +1551,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1560,7 +1561,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1570,7 +1571,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1580,7 +1581,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1590,7 +1591,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1600,7 +1601,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1610,7 +1611,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>

--- a/hall/resources/sample/PoolList.xlsx
+++ b/hall/resources/sample/PoolList.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -33,7 +38,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>卡池ID</t>
   </si>
@@ -91,6 +96,9 @@
     <t>卡池名称</t>
   </si>
   <si>
+    <t>名称备注</t>
+  </si>
+  <si>
     <t>卡池类型</t>
   </si>
   <si>
@@ -124,6 +132,9 @@
     <t>id</t>
   </si>
   <si>
+    <t>languageID</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -142,16 +153,16 @@
     <t>open</t>
   </si>
   <si>
-    <t>游客卡池1</t>
+    <t>幸运殿堂</t>
   </si>
   <si>
     <t>1024013_1</t>
   </si>
   <si>
-    <t>游客卡池2</t>
-  </si>
-  <si>
-    <t>雇员卡池1</t>
+    <t>霓虹名流</t>
+  </si>
+  <si>
+    <t>慧眼识珠</t>
   </si>
   <si>
     <t>1024014_1</t>
@@ -359,12 +370,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1382,15 +1393,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="4" max="4" width="20.25" customWidth="1"/>
-    <col min="5" max="5" width="18.5" customWidth="1"/>
-    <col min="6" max="6" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="11.125" customWidth="1"/>
+    <col min="5" max="5" width="20.25" customWidth="1"/>
+    <col min="6" max="6" width="18.5" customWidth="1"/>
+    <col min="7" max="7" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1415,56 +1427,65 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9">
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:10">
       <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="E2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="I2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>19</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1473,75 +1494,85 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="3">
         <v>10001</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="B5" s="3">
+        <v>4053073</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="3">
         <v>1001</v>
       </c>
-      <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3" t="b">
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" s="3">
         <v>10002</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B6" s="3">
+        <v>4053074</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="3">
         <v>1</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3">
         <v>1002</v>
       </c>
-      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3" t="b">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="3">
         <v>20001</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3">
-        <v>2</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="B7" s="3">
+        <v>4053076</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="3">
         <v>2001</v>
       </c>
-      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3" t="b">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1550,8 +1581,9 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1560,8 +1592,9 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1570,8 +1603,9 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1580,8 +1614,9 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1590,8 +1625,9 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1600,8 +1636,9 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1610,8 +1647,9 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1620,6 +1658,7 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1639,37 +1678,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:11">
